--- a/配置文件/配置.xlsx
+++ b/配置文件/配置.xlsx
@@ -191,7 +191,7 @@
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>从下拉选择得物起始路径（数据来自'得物类目库'）。
-匹配规则：程序拿商品 JSON 的 categoryName/categoryPath，逐个比对左侧关键词（包含即命中），最长关键词优先；都没命中则回落'基础设置-起始类目(兜底)'。</t>
+匹配规则：程序拿商品 JSON 的 categoryPath，逐个比对左侧关键词（包含即命中），最长关键词优先；都没命中则回落'基础设置-起始类目(兜底)'。</t>
       </text>
     </comment>
   </commentList>
@@ -537,7 +537,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>【尺码表】行=尺码，列=测量项。直接取代代码里写死的尺码表，请填实测值。</t>
+          <t>【尺码表】行=尺码，列=测量项。**列名必须与得物尺码弹窗的列名完全一致**（如 1/2胸围(cm)），否则填写时会报错；直接取代代码里写死的尺码表，请填实测值。</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  匹配规则（运行时）：拿商品 JSON 的 categoryName/categoryPath，逐个比对左侧关键词（包含即命中），'最长关键词优先'。</t>
+          <t xml:space="preserve">  匹配规则（运行时）：拿商品 JSON 的 categoryPath，逐个比对左侧关键词（包含即命中），'最长关键词优先'。</t>
         </is>
       </c>
     </row>
@@ -842,15 +842,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -861,27 +859,17 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>胸围</t>
+          <t>1/2胸围(cm)</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>衣长</t>
+          <t>衣长(cm)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>袖长</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>肩宽</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>腰围</t>
+          <t>袖长(cm)</t>
         </is>
       </c>
     </row>
@@ -891,20 +879,20 @@
           <t>M</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>50</v>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -913,20 +901,20 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>53</v>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -935,70 +923,70 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>56</v>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>XXL</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>59</v>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>XXXL</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>62</v>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>注：以上为临时估算值，请替换为实测数据；可增加/删除行。</t>
+          <t>注：以上为临时估算值，请替换为实测数据；列名须与得物尺码弹窗列名一致；可增加/删除行。</t>
         </is>
       </c>
     </row>

--- a/配置文件/配置.xlsx
+++ b/配置文件/配置.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="基础设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="包装尺寸" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="尺码表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="属性覆盖" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="得物类目库" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="类目映射" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基础设置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="包装尺寸" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尺码表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性覆盖" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="得物类目库" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="类目映射" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>【基础设置】标量项：出价类型/两个证明渠道/适用人群带下拉，其余自由填。'起始类目(兜底)'是类目映射都没命中时用的默认路径。</t>
+          <t>【基础设置】标量项：出价类型/两个证明渠道/适用人群带下拉，其余自由填。'起始类目(兜底)'是类目映射都没命中时用的默认路径，格式：一级&gt;&gt;二级&gt;&gt;三级（如 服装&gt;&gt;上衣&gt;&gt;卫衣）。</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>【得物类目库】从得物后台导出的完整类目树（服装+女装），是'类目映射'右侧目标路径的下拉来源，请勿手动修改其内容。</t>
+          <t>【得物类目库】从得物后台导出的完整类目树（服装+女装），是'类目映射'右侧目标路径的下拉来源，请勿手动修改其内容。注意：类目名本身可含“/”（如 三坑/COSPLAY），整条路径的层级分隔符是“&gt;&gt;”，不是“/”。</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  例：左侧填'卫衣'→ 右侧选'服装/上衣/卫衣'；左侧填'连帽卫衣'→ 右侧选'服装/上衣/卫衣'（连帽卫衣更长，优先于'卫衣'）。</t>
+          <t xml:space="preserve">  例：左侧填'卫衣'→ 右侧选'服装&gt;&gt;上衣&gt;&gt;卫衣'；左侧填'连帽卫衣'→ 右侧选'服装&gt;&gt;上衣&gt;&gt;卫衣'（连帽卫衣更长，优先于'卫衣'）。</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>服装/上衣/卫衣</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;卫衣</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/COSPLAY</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;COSPLAY</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/COS甲胄</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;COS甲胄</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita半身裙</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita半身裙</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita外套</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita外套</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita大衣</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita大衣</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita衬衫</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita衬衫</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita裤子</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita裤子</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/lolita连衣裙</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;lolita连衣裙</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/制服</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;制服</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/汉服</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;汉服</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/洋装</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;洋装</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/福瑞兽装</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;福瑞兽装</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>女装/三坑/COSPLAY/萝莉装</t>
+          <t>女装&gt;&gt;三坑/COSPLAY&gt;&gt;萝莉装</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/Polo衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;Polo衫</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/T恤</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;T恤</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/卫衣</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;卫衣</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/吊带</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;吊带</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/截短上衣</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;截短上衣</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/抹胸</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;抹胸</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/毛衣</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;毛衣</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/牛仔衬衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;牛仔衬衫</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/电竞服</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;电竞服</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/羊绒开衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;羊绒开衫</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/羊绒背心</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;羊绒背心</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/羊绒衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;羊绒衫</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/背心</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;背心</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/衬衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;衬衫</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/连体衣</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;连体衣</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/针织衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;针织衫</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>女装/上衣/雪纺衫</t>
+          <t>女装&gt;&gt;上衣&gt;&gt;雪纺衫</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>女装/中老年女装/中老年上装</t>
+          <t>女装&gt;&gt;中老年女装&gt;&gt;中老年上装</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>女装/中老年女装/中老年下装</t>
+          <t>女装&gt;&gt;中老年女装&gt;&gt;中老年下装</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/体操服</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;体操服</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/健美操服</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;健美操服</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/健身套装</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;健身套装</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/健身衣</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;健身衣</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/啦啦队服</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;啦啦队服</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽T恤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽T恤</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽内衣</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽内衣</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽外套</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽外套</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽套装</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽套装</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽短裙</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽短裙</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽短裤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽短裤</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽背心</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽背心</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽连体衣</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽连体衣</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/瑜伽长裤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;瑜伽长裤</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/训练防护服</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;训练防护服</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/运动内衣</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;运动内衣</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/运动短裤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;运动短裤</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/运动背心</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;运动背心</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/运动长裤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;运动长裤</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/骑行外套</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;骑行外套</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>女装/健身服/鲨鱼裤</t>
+          <t>女装&gt;&gt;健身服&gt;&gt;鲨鱼裤</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷T恤</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷T恤</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷吉利服</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷吉利服</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷大衣</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷大衣</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷夹克</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷夹克</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷工装裤</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷工装裤</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷服套装</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷服套装</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷羽绒服</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷羽绒服</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>女装/军迷作训服/军迷背心</t>
+          <t>女装&gt;&gt;军迷作训服&gt;&gt;军迷背心</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/冲锋衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;冲锋衣</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/含羽绒外套</t>
+          <t>女装&gt;&gt;外套&gt;&gt;含羽绒外套</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/大衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;大衣</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/夹克</t>
+          <t>女装&gt;&gt;外套&gt;&gt;夹克</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/截短外套</t>
+          <t>女装&gt;&gt;外套&gt;&gt;截短外套</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/斗篷披风</t>
+          <t>女装&gt;&gt;外套&gt;&gt;斗篷披风</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/棉服</t>
+          <t>女装&gt;&gt;外套&gt;&gt;棉服</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/棒球服</t>
+          <t>女装&gt;&gt;外套&gt;&gt;棒球服</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/派克服</t>
+          <t>女装&gt;&gt;外套&gt;&gt;派克服</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/牛仔外套</t>
+          <t>女装&gt;&gt;外套&gt;&gt;牛仔外套</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/皮肤衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;皮肤衣</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/皮草</t>
+          <t>女装&gt;&gt;外套&gt;&gt;皮草</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/皮衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;皮衣</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/绒感外套</t>
+          <t>女装&gt;&gt;外套&gt;&gt;绒感外套</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/羽绒服</t>
+          <t>女装&gt;&gt;外套&gt;&gt;羽绒服</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/羽绒马甲</t>
+          <t>女装&gt;&gt;外套&gt;&gt;羽绒马甲</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/西装</t>
+          <t>女装&gt;&gt;外套&gt;&gt;西装</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/软壳衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;软壳衣</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/防晒服</t>
+          <t>女装&gt;&gt;外套&gt;&gt;防晒服</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/风衣</t>
+          <t>女装&gt;&gt;外套&gt;&gt;风衣</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>女装/外套/马甲</t>
+          <t>女装&gt;&gt;外套&gt;&gt;马甲</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/休闲套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;休闲套装</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/冲锋衣裤套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;冲锋衣裤套装</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/卫衣套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;卫衣套装</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/情侣套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;情侣套装</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/职业裙装套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;职业裙装套装</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/职业裤装套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;职业裤装套装</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/衬衫套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;衬衫套装</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/裙装套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;裙装套装</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/西装套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;西装套装</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/软壳衣裤套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;软壳衣裤套装</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>女装/女装套装/闺蜜套装</t>
+          <t>女装&gt;&gt;女装套装&gt;&gt;闺蜜套装</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>女装/婚纱/旗袍/礼服/婚纱</t>
+          <t>女装&gt;&gt;婚纱/旗袍/礼服&gt;&gt;婚纱</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>女装/婚纱/旗袍/礼服/旗袍</t>
+          <t>女装&gt;&gt;婚纱/旗袍/礼服&gt;&gt;旗袍</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>女装/婚纱/旗袍/礼服/礼服</t>
+          <t>女装&gt;&gt;婚纱/旗袍/礼服&gt;&gt;礼服</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/军迷服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;军迷服</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/冲浪服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;冲浪服</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/冲浪防寒衣</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;冲浪防寒衣</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/抓绒衣</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;抓绒衣</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/抓绒裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;抓绒裤</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/滑冰服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;滑冰服</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/滑雪衣</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;滑雪衣</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/滑雪衣套装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;滑雪衣套装</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/滑雪裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;滑雪裤</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/田径服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;田径服</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/登山服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;登山服</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/赛车T恤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;赛车T恤</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/赛车套装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;赛车套装</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/赛车服/机车服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;赛车服/机车服</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/赛车裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;赛车裤</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步T恤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步T恤</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步外套</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步外套</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步服套装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步服套装</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步短裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步短裤</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步背心</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步背心</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步长裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步长裤</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/跑步马甲</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;跑步马甲</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/运动保暖内衣</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;运动保暖内衣</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/连体滑雪服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;连体滑雪服</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/连体骑行服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;连体骑行服</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/速干T恤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;速干T恤</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/速干背心</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;速干背心</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/速干衣</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;速干衣</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/速干衣裤套装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;速干衣裤套装</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/速干裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;速干裤</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/钓鱼服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;钓鱼服</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/风壳</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;风壳</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/马术装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;马术装</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行内搭</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行内搭</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行内裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行内裤</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行套装</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行套装</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行服</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行服</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行裤</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行裤</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>女装/户外运动服/骑行马甲</t>
+          <t>女装&gt;&gt;户外运动服&gt;&gt;骑行马甲</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/剑道服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;剑道服</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/太极服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;太极服</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/拳击服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;拳击服</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/摔跤服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;摔跤服</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/柔道服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;柔道服</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/空手道服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;空手道服</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>女装/武术搏击服/跆拳道服</t>
+          <t>女装&gt;&gt;武术搏击服&gt;&gt;跆拳道服</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/唐装</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;唐装</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/汉服上装</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;汉服上装</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/汉服半身裙</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;汉服半身裙</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/汉服套装</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;汉服套装</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/汉服裤装</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;汉服裤装</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/汉服连衣裙</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;汉服连衣裙</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>女装/民族服装/秀禾服</t>
+          <t>女装&gt;&gt;民族服装&gt;&gt;秀禾服</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/分体泳衣</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;分体泳衣</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/比基尼</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;比基尼</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/沙滩裤</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;沙滩裤</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/泳衣套装</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;泳衣套装</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/泳装裙</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;泳装裙</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/泳裤</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;泳裤</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/潜水服</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;潜水服</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/裹裙/披纱</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;裹裙/披纱</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/连体泳装</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;连体泳装</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>女装/泳装/速干袍</t>
+          <t>女装&gt;&gt;泳装&gt;&gt;速干袍</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/乒乓球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;乒乓球服</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/乒乓球服套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;乒乓球服套装</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/其他球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;其他球服</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/匹克球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;匹克球服</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/排球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;排球服</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/橄榄球下装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;橄榄球下装</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/橄榄球套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;橄榄球套装</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/橄榄球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;橄榄球服</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/篮球套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;篮球套装</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/篮球背心</t>
+          <t>女装&gt;&gt;球服&gt;&gt;篮球背心</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/篮球衣</t>
+          <t>女装&gt;&gt;球服&gt;&gt;篮球衣</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/篮球裤</t>
+          <t>女装&gt;&gt;球服&gt;&gt;篮球裤</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/网球套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;网球套装</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/网球衣</t>
+          <t>女装&gt;&gt;球服&gt;&gt;网球衣</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/网球裙</t>
+          <t>女装&gt;&gt;球服&gt;&gt;网球裙</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/网球裤</t>
+          <t>女装&gt;&gt;球服&gt;&gt;网球裤</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/羽毛球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;羽毛球服</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/羽毛球服套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;羽毛球服套装</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/羽毛球裙</t>
+          <t>女装&gt;&gt;球服&gt;&gt;羽毛球裙</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/羽毛球裤</t>
+          <t>女装&gt;&gt;球服&gt;&gt;羽毛球裤</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/足球套装</t>
+          <t>女装&gt;&gt;球服&gt;&gt;足球套装</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/足球衣</t>
+          <t>女装&gt;&gt;球服&gt;&gt;足球衣</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/足球裤</t>
+          <t>女装&gt;&gt;球服&gt;&gt;足球裤</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>女装/球服/高尔夫球服</t>
+          <t>女装&gt;&gt;球服&gt;&gt;高尔夫球服</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>女装/盲盒/礼盒/女装盲盒</t>
+          <t>女装&gt;&gt;盲盒/礼盒&gt;&gt;女装盲盒</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>女装/盲盒/礼盒/女装礼盒</t>
+          <t>女装&gt;&gt;盲盒/礼盒&gt;&gt;女装礼盒</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>女装/短裙/休闲短裙</t>
+          <t>女装&gt;&gt;短裙&gt;&gt;休闲短裙</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>女装/短裙/屁帘</t>
+          <t>女装&gt;&gt;短裙&gt;&gt;屁帘</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>女装/短裙/工装短裙</t>
+          <t>女装&gt;&gt;短裙&gt;&gt;工装短裙</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>女装/短裙/牛仔短裙</t>
+          <t>女装&gt;&gt;短裙&gt;&gt;牛仔短裙</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>女装/短裙/皮短裙</t>
+          <t>女装&gt;&gt;短裙&gt;&gt;皮短裙</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>女装/短裤/休闲短裤</t>
+          <t>女装&gt;&gt;短裤&gt;&gt;休闲短裤</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>女装/短裤/工装短裤</t>
+          <t>女装&gt;&gt;短裤&gt;&gt;工装短裤</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>女装/短裤/牛仔短裤</t>
+          <t>女装&gt;&gt;短裤&gt;&gt;牛仔短裤</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/傣族舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;傣族舞服</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/古典舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;古典舞服</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/广场舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;广场舞服</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/拉丁舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;拉丁舞服</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/摩登舞上装</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;摩登舞上装</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/摩登舞下装</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;摩登舞下装</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/摩登舞套装</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;摩登舞套装</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/新疆舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;新疆舞服</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/朝鲜舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;朝鲜舞服</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/爵士舞服装</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;爵士舞服装</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/现代舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;现代舞服</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/秧歌服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;秧歌服</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/肚皮舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;肚皮舞服</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/芭蕾舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;芭蕾舞服</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/草裙舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;草裙舞服</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/藏族舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;藏族舞服</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/踢踏舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;踢踏舞服</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>女装/舞蹈服/钢管舞服</t>
+          <t>女装&gt;&gt;舞蹈服&gt;&gt;钢管舞服</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>女装/连衣裙/吊带连衣裙</t>
+          <t>女装&gt;&gt;连衣裙&gt;&gt;吊带连衣裙</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>女装/连衣裙/无袖连衣裙</t>
+          <t>女装&gt;&gt;连衣裙&gt;&gt;无袖连衣裙</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>女装/连衣裙/短袖连衣裙</t>
+          <t>女装&gt;&gt;连衣裙&gt;&gt;短袖连衣裙</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>女装/连衣裙/长袖连衣裙</t>
+          <t>女装&gt;&gt;连衣裙&gt;&gt;长袖连衣裙</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>女装/长裙/休闲长裙</t>
+          <t>女装&gt;&gt;长裙&gt;&gt;休闲长裙</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>女装/长裙/牛仔长裙</t>
+          <t>女装&gt;&gt;长裙&gt;&gt;牛仔长裙</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>女装/长裙/皮长裙</t>
+          <t>女装&gt;&gt;长裙&gt;&gt;皮长裙</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>女装/长裙/针织长裙</t>
+          <t>女装&gt;&gt;长裙&gt;&gt;针织长裙</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/休闲裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;休闲裤</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/冲锋裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;冲锋裤</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/工装裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;工装裤</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/打底裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;打底裤</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/棉裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;棉裤</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/牛仔裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;牛仔裤</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/皮裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;皮裤</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/羽绒裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;羽绒裤</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/背带裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;背带裤</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/西装裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;西装裤</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/软壳裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;软壳裤</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/连体裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;连体裤</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/针织运动裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;针织运动裤</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>女装/长裤/防晒裤</t>
+          <t>女装&gt;&gt;长裤&gt;&gt;防晒裤</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>服装/三坑/COSPLAY/COSPLAY</t>
+          <t>服装&gt;&gt;三坑/COSPLAY&gt;&gt;COSPLAY</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>服装/三坑/COSPLAY/COS甲胄</t>
+          <t>服装&gt;&gt;三坑/COSPLAY&gt;&gt;COS甲胄</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>服装/三坑/COSPLAY/制服</t>
+          <t>服装&gt;&gt;三坑/COSPLAY&gt;&gt;制服</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>服装/三坑/COSPLAY/汉服</t>
+          <t>服装&gt;&gt;三坑/COSPLAY&gt;&gt;汉服</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>服装/三坑/COSPLAY/福瑞兽装</t>
+          <t>服装&gt;&gt;三坑/COSPLAY&gt;&gt;福瑞兽装</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/Polo衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;Polo衫</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/T恤</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;T恤</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/卫衣</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;卫衣</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/吊带</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;吊带</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/毛衣</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;毛衣</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/牛仔衬衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;牛仔衬衫</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/电竞服</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;电竞服</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/羊绒开衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;羊绒开衫</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/羊绒背心</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;羊绒背心</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/羊绒衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;羊绒衫</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/背心</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;背心</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/衬衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;衬衫</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>服装/上衣/针织衫</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;针织衫</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>服装/中老年男装/中老年上装</t>
+          <t>服装&gt;&gt;中老年男装&gt;&gt;中老年上装</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>服装/中老年男装/中老年下装</t>
+          <t>服装&gt;&gt;中老年男装&gt;&gt;中老年下装</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>服装/中老年男装/中老年套装</t>
+          <t>服装&gt;&gt;中老年男装&gt;&gt;中老年套装</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/体操服</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;体操服</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/健美操服</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;健美操服</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/健身套装</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;健身套装</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/健身衣</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;健身衣</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/啦啦队服</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;啦啦队服</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/瑜伽T恤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;瑜伽T恤</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/瑜伽短裤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;瑜伽短裤</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/瑜伽长裤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;瑜伽长裤</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/训练防护服</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;训练防护服</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/运动短裤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;运动短裤</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/运动长裤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;运动长裤</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>服装/健身服/鲨鱼裤</t>
+          <t>服装&gt;&gt;健身服&gt;&gt;鲨鱼裤</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷T恤</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷T恤</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷吉利服</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷吉利服</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷大衣</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷大衣</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷夹克</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷夹克</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷工装裤</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷工装裤</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷服套装</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷服套装</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷羽绒服</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷羽绒服</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>服装/军迷作训服/军迷背心</t>
+          <t>服装&gt;&gt;军迷作训服&gt;&gt;军迷背心</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>服装/加价购/刻字服务</t>
+          <t>服装&gt;&gt;加价购&gt;&gt;刻字服务</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>服装/加价购/服装周边</t>
+          <t>服装&gt;&gt;加价购&gt;&gt;服装周边</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>服装/加价购/服装定制</t>
+          <t>服装&gt;&gt;加价购&gt;&gt;服装定制</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/中山装</t>
+          <t>服装&gt;&gt;外套&gt;&gt;中山装</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/冲锋衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;冲锋衣</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/含羽绒外套</t>
+          <t>服装&gt;&gt;外套&gt;&gt;含羽绒外套</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/大衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;大衣</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/夹克</t>
+          <t>服装&gt;&gt;外套&gt;&gt;夹克</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/斗篷披风</t>
+          <t>服装&gt;&gt;外套&gt;&gt;斗篷披风</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/棉服</t>
+          <t>服装&gt;&gt;外套&gt;&gt;棉服</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/棒球服</t>
+          <t>服装&gt;&gt;外套&gt;&gt;棒球服</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/派克服</t>
+          <t>服装&gt;&gt;外套&gt;&gt;派克服</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/牛仔外套</t>
+          <t>服装&gt;&gt;外套&gt;&gt;牛仔外套</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/皮肤衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;皮肤衣</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/皮草</t>
+          <t>服装&gt;&gt;外套&gt;&gt;皮草</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/皮衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;皮衣</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/绒感外套</t>
+          <t>服装&gt;&gt;外套&gt;&gt;绒感外套</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/羽绒服</t>
+          <t>服装&gt;&gt;外套&gt;&gt;羽绒服</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/羽绒马甲</t>
+          <t>服装&gt;&gt;外套&gt;&gt;羽绒马甲</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/西装</t>
+          <t>服装&gt;&gt;外套&gt;&gt;西装</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/软壳衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;软壳衣</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/防晒服</t>
+          <t>服装&gt;&gt;外套&gt;&gt;防晒服</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/风衣</t>
+          <t>服装&gt;&gt;外套&gt;&gt;风衣</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>服装/外套/马甲</t>
+          <t>服装&gt;&gt;外套&gt;&gt;马甲</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>服装/大码男装/大码上装</t>
+          <t>服装&gt;&gt;大码男装&gt;&gt;大码上装</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>服装/大码男装/大码下装</t>
+          <t>服装&gt;&gt;大码男装&gt;&gt;大码下装</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>服装/大码男装/大码套装</t>
+          <t>服装&gt;&gt;大码男装&gt;&gt;大码套装</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/军迷服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;军迷服</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/冲浪服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;冲浪服</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/冲浪防寒衣</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;冲浪防寒衣</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/抓绒衣</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;抓绒衣</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/抓绒裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;抓绒裤</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/滑冰服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;滑冰服</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/滑雪衣</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;滑雪衣</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/滑雪衣套装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;滑雪衣套装</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/滑雪裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;滑雪裤</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/田径服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;田径服</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/登山服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;登山服</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/赛车T恤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;赛车T恤</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/赛车套装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;赛车套装</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/赛车服/机车服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;赛车服/机车服</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/赛车裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;赛车裤</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步T恤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步T恤</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步外套</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步外套</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步服套装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步服套装</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步短裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步短裤</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步背心</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步背心</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步长裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步长裤</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/跑步马甲</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;跑步马甲</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/运动保暖内衣</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;运动保暖内衣</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/连体滑雪服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;连体滑雪服</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/连体骑行服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;连体骑行服</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/速干T恤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;速干T恤</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/速干背心</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;速干背心</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/速干衣</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;速干衣</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/速干衣裤套装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;速干衣裤套装</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/速干裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;速干裤</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/钓鱼服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;钓鱼服</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/风壳</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;风壳</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/马术装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;马术装</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行内搭</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行内搭</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行内裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行内裤</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行外套</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行外套</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行套装</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行套装</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行服</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行服</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行裤</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行裤</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>服装/户外运动服/骑行马甲</t>
+          <t>服装&gt;&gt;户外运动服&gt;&gt;骑行马甲</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/休闲运动套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;休闲运动套装</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/冲锋衣裤套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;冲锋衣裤套装</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/卫衣套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;卫衣套装</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/情侣套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;情侣套装</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/衬衫套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;衬衫套装</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="D348" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/西装套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;西装套装</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>服装/服装套装/软壳衣裤套装</t>
+          <t>服装&gt;&gt;服装套装&gt;&gt;软壳衣裤套装</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="D350" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/剑道服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;剑道服</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/太极服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;太极服</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/拳击服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;拳击服</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/摔跤服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;摔跤服</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/柔道服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;柔道服</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/空手道服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;空手道服</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>服装/武术搏击服/跆拳道服</t>
+          <t>服装&gt;&gt;武术搏击服&gt;&gt;跆拳道服</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/其他民族服装</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;其他民族服装</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/唐装</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;唐装</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/汉服上装</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;汉服上装</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/汉服套装</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;汉服套装</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/汉服裤装</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;汉服裤装</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="D362" s="8" t="inlineStr">
         <is>
-          <t>服装/民族服装/秀禾服</t>
+          <t>服装&gt;&gt;民族服装&gt;&gt;秀禾服</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/沙滩裤</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;沙滩裤</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/泳衣套装</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;泳衣套装</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/泳裤</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;泳裤</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/潜水服</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;潜水服</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/男士泳装</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;男士泳装</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D368" s="8" t="inlineStr">
         <is>
-          <t>服装/泳装/速干袍</t>
+          <t>服装&gt;&gt;泳装&gt;&gt;速干袍</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/乒乓球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;乒乓球服</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D370" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/乒乓球服套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;乒乓球服套装</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/其他球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;其他球服</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="D372" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/匹克球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;匹克球服</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/排球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;排球服</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/橄榄球下装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;橄榄球下装</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/橄榄球套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;橄榄球套装</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/橄榄球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;橄榄球服</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/篮球套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;篮球套装</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/篮球背心</t>
+          <t>服装&gt;&gt;球服&gt;&gt;篮球背心</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/篮球衣</t>
+          <t>服装&gt;&gt;球服&gt;&gt;篮球衣</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/篮球裤</t>
+          <t>服装&gt;&gt;球服&gt;&gt;篮球裤</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/网球下装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;网球下装</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/网球套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;网球套装</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/网球衣</t>
+          <t>服装&gt;&gt;球服&gt;&gt;网球衣</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/羽毛球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;羽毛球服</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/羽毛球服套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;羽毛球服套装</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/羽毛球裤</t>
+          <t>服装&gt;&gt;球服&gt;&gt;羽毛球裤</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/足球套装</t>
+          <t>服装&gt;&gt;球服&gt;&gt;足球套装</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="D388" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/足球衣</t>
+          <t>服装&gt;&gt;球服&gt;&gt;足球衣</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/足球裤</t>
+          <t>服装&gt;&gt;球服&gt;&gt;足球裤</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="D390" s="8" t="inlineStr">
         <is>
-          <t>服装/球服/高尔夫球服</t>
+          <t>服装&gt;&gt;球服&gt;&gt;高尔夫球服</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>服装/盲盒/礼盒/服装盲盒</t>
+          <t>服装&gt;&gt;盲盒/礼盒&gt;&gt;服装盲盒</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="D392" s="8" t="inlineStr">
         <is>
-          <t>服装/盲盒/礼盒/服装礼盒</t>
+          <t>服装&gt;&gt;盲盒/礼盒&gt;&gt;服装礼盒</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>服装/短裤/休闲短裤</t>
+          <t>服装&gt;&gt;短裤&gt;&gt;休闲短裤</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="D394" s="8" t="inlineStr">
         <is>
-          <t>服装/短裤/工装短裤</t>
+          <t>服装&gt;&gt;短裤&gt;&gt;工装短裤</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>服装/短裤/牛仔短裤</t>
+          <t>服装&gt;&gt;短裤&gt;&gt;牛仔短裤</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="D396" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/傣族舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;傣族舞服</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/古典舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;古典舞服</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/广场舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;广场舞服</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/拉丁舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;拉丁舞服</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/新疆舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;新疆舞服</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/朝鲜舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;朝鲜舞服</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/爵士舞服装</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;爵士舞服装</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/秧歌服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;秧歌服</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/肚皮舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;肚皮舞服</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/芭蕾舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;芭蕾舞服</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/草裙舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;草裙舞服</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/藏族舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;藏族舞服</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>服装/舞蹈服/踢踏舞服</t>
+          <t>服装&gt;&gt;舞蹈服&gt;&gt;踢踏舞服</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>服装/裙子/半身裙</t>
+          <t>服装&gt;&gt;裙子&gt;&gt;半身裙</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/休闲裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;休闲裤</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/冲锋裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;冲锋裤</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/工装裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;工装裤</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/棉裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;棉裤</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D414" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/牛仔裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;牛仔裤</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/皮裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;皮裤</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="D416" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/羽绒裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;羽绒裤</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/背带裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;背带裤</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/西装裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;西装裤</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/软壳裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;软壳裤</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/连体裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;连体裤</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/针织运动裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;针织运动裤</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>服装/长裤/防晒裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;防晒裤</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>服装/上衣/卫衣</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;卫衣</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>服装/上衣/卫衣</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;卫衣</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>服装/上衣/T恤</t>
+          <t>服装&gt;&gt;上衣&gt;&gt;T恤</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>服装/长裤/牛仔裤</t>
+          <t>服装&gt;&gt;长裤&gt;&gt;牛仔裤</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
